--- a/config/_tables/tables__.xlsx
+++ b/config/_tables/tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31900" windowHeight="15700"/>
+    <workbookView windowWidth="18040" windowHeight="13030"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
     <t>GameGlobal</t>
   </si>
   <si>
-    <t>Global</t>
+    <t>TbGlobal</t>
   </si>
   <si>
     <t>_Global.xlsx</t>
